--- a/data/csv/Changchun_Precise_Points.xlsx
+++ b/data/csv/Changchun_Precise_Points.xlsx
@@ -1,37 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Lng</t>
+  </si>
+  <si>
+    <t>Lat</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +63,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,5070 +379,5060 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C459"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Lng</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>125.3398763000001</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>43.89209257027027</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>125.3406263000001</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>43.89236284054054</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>8</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>125.3395013000001</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>43.89263311081081</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>13</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>125.3413763000001</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>43.89263311081081</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>18</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>125.3402513000001</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>43.89290338108108</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>23</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>125.3421263000001</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>43.89290338108108</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>25</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>125.3391263000001</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>43.89317365135135</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>30</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>125.3410013000001</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>43.89317365135135</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>35</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>125.3428763000002</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>43.89317365135135</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>40</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>125.3398763000001</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>43.89344392162162</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>45</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>125.3417513000001</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>43.89344392162162</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>50</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>125.3436263000002</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>43.89344392162162</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>52</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>125.3443763000002</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>43.89344392162162</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>53</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>125.3387513000001</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>43.8937141918919</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>58</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>125.3406263000001</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>43.8937141918919</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>63</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>125.3425013000002</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>43.8937141918919</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>70</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>125.3451263000002</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>43.8937141918919</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>74</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>125.3395013000001</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>43.89398446216217</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>79</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>125.3413763000001</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>43.89398446216217</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>84</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>125.3432513000002</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>43.89398446216217</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>86</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>125.3440013000002</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>43.89398446216217</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>91</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>125.3458763000002</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>43.89398446216217</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>92</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>125.3383763000001</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>43.89425473243244</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>97</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>125.3402513000001</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>43.89425473243244</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>102</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>125.3421263000001</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>43.89425473243244</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>109</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>125.3447513000002</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>43.89425473243244</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>114</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>125.3466263000002</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>43.89425473243244</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>118</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>125.3391263000001</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>43.89452500270271</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>123</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>125.3410013000001</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>43.89452500270271</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>128</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>125.3428763000002</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>43.89452500270271</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>130</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>125.3436263000002</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>43.89452500270271</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>135</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>125.3455013000002</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>43.89452500270271</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>140</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>125.3473763000002</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>43.89452500270271</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>141</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>125.3380013000001</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>43.89479527297298</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>146</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>125.3398763000001</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>43.89479527297298</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>151</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>125.3417513000001</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>43.89479527297298</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>158</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>125.3443763000002</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>43.89479527297298</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>163</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>125.3462513000002</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>43.89479527297298</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>168</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>125.3481263000002</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>43.89479527297298</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>172</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>125.3387513000001</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>43.89506554324325</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>177</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>125.3406263000001</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>43.89506554324325</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>182</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>125.3425013000002</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>43.89506554324325</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>184</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>125.3432513000002</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>43.89506554324325</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>189</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>125.3451263000002</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>43.89506554324325</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>194</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>125.3470013000002</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>43.89506554324325</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>199</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>125.3488763000002</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>43.89506554324325</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>200</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>125.3376263000001</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>43.89533581351352</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>205</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>125.3395013000001</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>43.89533581351352</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>210</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>125.3413763000001</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>43.89533581351352</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>217</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>125.3440013000002</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>43.89533581351352</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>222</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>125.3458763000002</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>43.89533581351352</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>227</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>125.3477513000002</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>43.89533581351352</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>235</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>125.3383763000001</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:3">
+      <c r="A55">
         <v>240</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>125.3402513000001</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:3">
+      <c r="A56">
         <v>245</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>125.3421263000001</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:3">
+      <c r="A57">
         <v>247</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>125.3428763000002</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:3">
+      <c r="A58">
         <v>252</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>125.3447513000002</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:3">
+      <c r="A59">
         <v>257</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>125.3466263000002</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:3">
+      <c r="A60">
         <v>262</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>125.3485013000002</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:3">
+      <c r="A61">
         <v>264</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>125.3492513000002</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>43.89560608378379</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:3">
+      <c r="A62">
         <v>265</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>125.3372513000001</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>43.89587635405406</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:3">
+      <c r="A63">
         <v>270</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>125.3391263000001</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>43.89587635405406</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:3">
+      <c r="A64">
         <v>275</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>125.3410013000001</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>43.89587635405406</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:3">
+      <c r="A65">
         <v>282</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>125.3436263000002</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>43.89587635405406</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:3">
+      <c r="A66">
         <v>287</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>125.3455013000002</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>43.89587635405406</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:3">
+      <c r="A67">
         <v>292</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>125.3473763000002</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>43.89587635405406</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:3">
+      <c r="A68">
         <v>301</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>125.3380013000001</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:3">
+      <c r="A69">
         <v>306</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>125.3398763000001</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:3">
+      <c r="A70">
         <v>311</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>125.3417513000001</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:3">
+      <c r="A71">
         <v>313</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>125.3425013000002</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:3">
+      <c r="A72">
         <v>318</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>125.3443763000002</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:3">
+      <c r="A73">
         <v>323</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>125.3462513000002</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:3">
+      <c r="A74">
         <v>328</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>125.3481263000002</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:3">
+      <c r="A75">
         <v>330</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>125.3488763000002</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:3">
+      <c r="A76">
         <v>332</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>125.3496263000003</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>43.89614662432433</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:3">
+      <c r="A77">
         <v>333</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>125.3368763000001</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>43.8964168945946</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:3">
+      <c r="A78">
         <v>338</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>125.3387513000001</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>43.8964168945946</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:3">
+      <c r="A79">
         <v>343</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>125.3406263000001</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>43.8964168945946</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:3">
+      <c r="A80">
         <v>350</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>125.3432513000002</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>43.8964168945946</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:3">
+      <c r="A81">
         <v>355</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>125.3451263000002</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>43.8964168945946</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:3">
+      <c r="A82">
         <v>360</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>125.3470013000002</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>43.8964168945946</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:3">
+      <c r="A83">
         <v>371</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>125.3376263000001</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:3">
+      <c r="A84">
         <v>376</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>125.3395013000001</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:3">
+      <c r="A85">
         <v>381</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>125.3413763000001</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:3">
+      <c r="A86">
         <v>383</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>125.3421263000001</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:3">
+      <c r="A87">
         <v>388</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>125.3440013000002</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:3">
+      <c r="A88">
         <v>393</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>125.3458763000002</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:3">
+      <c r="A89">
         <v>398</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>125.3477513000002</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:3">
+      <c r="A90">
         <v>400</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>125.3485013000002</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:3">
+      <c r="A91">
         <v>402</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>125.3492513000002</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:3">
+      <c r="A92">
         <v>404</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>125.3500013000003</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>43.89668716486487</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:3">
+      <c r="A93">
         <v>406</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>125.3365013000001</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>43.89695743513514</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:3">
+      <c r="A94">
         <v>411</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>125.3383763000001</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>43.89695743513514</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:3">
+      <c r="A95">
         <v>416</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>125.3402513000001</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>43.89695743513514</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:3">
+      <c r="A96">
         <v>423</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>125.3428763000002</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>43.89695743513514</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:3">
+      <c r="A97">
         <v>428</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>125.3447513000002</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>43.89695743513514</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:3">
+      <c r="A98">
         <v>433</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>125.3466263000002</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>43.89695743513514</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:3">
+      <c r="A99">
         <v>444</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>125.3507513000003</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>43.89695743513514</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:3">
+      <c r="A100">
         <v>447</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>125.3372513000001</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:3">
+      <c r="A101">
         <v>452</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>125.3391263000001</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:3">
+      <c r="A102">
         <v>457</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>125.3410013000001</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:3">
+      <c r="A103">
         <v>459</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>125.3417513000001</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:3">
+      <c r="A104">
         <v>464</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>125.3436263000002</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:3">
+      <c r="A105">
         <v>469</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>125.3455013000002</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:3">
+      <c r="A106">
         <v>474</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>125.3473763000002</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="107" spans="1:3">
+      <c r="A107">
         <v>476</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107">
         <v>125.3481263000002</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:3">
+      <c r="A108">
         <v>478</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>125.3488763000002</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:3">
+      <c r="A109">
         <v>480</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>125.3496263000003</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>43.89722770540541</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:3">
+      <c r="A110">
         <v>484</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>125.3361263000001</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110">
         <v>43.89749797567568</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:3">
+      <c r="A111">
         <v>489</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>125.3380013000001</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111">
         <v>43.89749797567568</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:3">
+      <c r="A112">
         <v>494</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>125.3398763000001</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112">
         <v>43.89749797567568</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:3">
+      <c r="A113">
         <v>501</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>125.3425013000002</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113">
         <v>43.89749797567568</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:3">
+      <c r="A114">
         <v>506</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114">
         <v>125.3443763000002</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114">
         <v>43.89749797567568</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="n">
+    <row r="115" spans="1:3">
+      <c r="A115">
         <v>511</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>125.3462513000002</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115">
         <v>43.89749797567568</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
+    <row r="116" spans="1:3">
+      <c r="A116">
         <v>522</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>125.3503763000003</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>43.89749797567568</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="n">
+    <row r="117" spans="1:3">
+      <c r="A117">
         <v>525</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>125.3368763000001</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="n">
+    <row r="118" spans="1:3">
+      <c r="A118">
         <v>530</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>125.3387513000001</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="n">
+    <row r="119" spans="1:3">
+      <c r="A119">
         <v>535</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119">
         <v>125.3406263000001</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="n">
+    <row r="120" spans="1:3">
+      <c r="A120">
         <v>537</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120">
         <v>125.3413763000001</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="n">
+    <row r="121" spans="1:3">
+      <c r="A121">
         <v>542</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121">
         <v>125.3432513000002</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="n">
+    <row r="122" spans="1:3">
+      <c r="A122">
         <v>547</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122">
         <v>125.3451263000002</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="n">
+    <row r="123" spans="1:3">
+      <c r="A123">
         <v>552</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123">
         <v>125.3470013000002</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="124" spans="1:3">
+      <c r="A124">
         <v>554</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124">
         <v>125.3477513000002</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
+    <row r="125" spans="1:3">
+      <c r="A125">
         <v>556</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125">
         <v>125.3485013000002</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
+    <row r="126" spans="1:3">
+      <c r="A126">
         <v>558</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126">
         <v>125.3492513000002</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126">
         <v>43.89776824594595</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="n">
+    <row r="127" spans="1:3">
+      <c r="A127">
         <v>562</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127">
         <v>125.3357513000001</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127">
         <v>43.89803851621622</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="n">
+    <row r="128" spans="1:3">
+      <c r="A128">
         <v>567</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128">
         <v>125.3376263000001</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128">
         <v>43.89803851621622</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="n">
+    <row r="129" spans="1:3">
+      <c r="A129">
         <v>572</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129">
         <v>125.3395013000001</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129">
         <v>43.89803851621622</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="n">
+    <row r="130" spans="1:3">
+      <c r="A130">
         <v>579</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130">
         <v>125.3421263000001</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130">
         <v>43.89803851621622</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="n">
+    <row r="131" spans="1:3">
+      <c r="A131">
         <v>584</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131">
         <v>125.3440013000002</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131">
         <v>43.89803851621622</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="n">
+    <row r="132" spans="1:3">
+      <c r="A132">
         <v>589</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132">
         <v>125.3458763000002</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132">
         <v>43.89803851621622</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="n">
+    <row r="133" spans="1:3">
+      <c r="A133">
         <v>600</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133">
         <v>125.3500013000003</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133">
         <v>43.89803851621622</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="n">
+    <row r="134" spans="1:3">
+      <c r="A134">
         <v>603</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134">
         <v>125.3365013000001</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="n">
+    <row r="135" spans="1:3">
+      <c r="A135">
         <v>608</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135">
         <v>125.3383763000001</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="n">
+    <row r="136" spans="1:3">
+      <c r="A136">
         <v>613</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136">
         <v>125.3402513000001</v>
       </c>
-      <c r="C136" t="n">
+      <c r="C136">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="n">
+    <row r="137" spans="1:3">
+      <c r="A137">
         <v>615</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137">
         <v>125.3410013000001</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="n">
+    <row r="138" spans="1:3">
+      <c r="A138">
         <v>620</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138">
         <v>125.3428763000002</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="n">
+    <row r="139" spans="1:3">
+      <c r="A139">
         <v>625</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139">
         <v>125.3447513000002</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C139">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="n">
+    <row r="140" spans="1:3">
+      <c r="A140">
         <v>630</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140">
         <v>125.3466263000002</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="n">
+    <row r="141" spans="1:3">
+      <c r="A141">
         <v>632</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141">
         <v>125.3473763000002</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="n">
+    <row r="142" spans="1:3">
+      <c r="A142">
         <v>634</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142">
         <v>125.3481263000002</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="n">
+    <row r="143" spans="1:3">
+      <c r="A143">
         <v>636</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143">
         <v>125.3488763000002</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C143">
         <v>43.8983087864865</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="144" spans="1:3">
+      <c r="A144">
         <v>639</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144">
         <v>125.3353763</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144">
         <v>43.89857905675677</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="n">
+    <row r="145" spans="1:3">
+      <c r="A145">
         <v>644</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B145">
         <v>125.3372513000001</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145">
         <v>43.89857905675677</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="n">
+    <row r="146" spans="1:3">
+      <c r="A146">
         <v>649</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146">
         <v>125.3391263000001</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146">
         <v>43.89857905675677</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
+    <row r="147" spans="1:3">
+      <c r="A147">
         <v>656</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147">
         <v>125.3417513000001</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147">
         <v>43.89857905675677</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="148" spans="1:3">
+      <c r="A148">
         <v>661</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148">
         <v>125.3436263000002</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148">
         <v>43.89857905675677</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="149" spans="1:3">
+      <c r="A149">
         <v>666</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149">
         <v>125.3455013000002</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149">
         <v>43.89857905675677</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="150" spans="1:3">
+      <c r="A150">
         <v>680</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150">
         <v>125.3361263000001</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C150">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="n">
+    <row r="151" spans="1:3">
+      <c r="A151">
         <v>685</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151">
         <v>125.3380013000001</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="n">
+    <row r="152" spans="1:3">
+      <c r="A152">
         <v>690</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152">
         <v>125.3398763000001</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C152">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="n">
+    <row r="153" spans="1:3">
+      <c r="A153">
         <v>692</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153">
         <v>125.3406263000001</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="n">
+    <row r="154" spans="1:3">
+      <c r="A154">
         <v>697</v>
       </c>
-      <c r="B154" t="n">
+      <c r="B154">
         <v>125.3425013000002</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="n">
+    <row r="155" spans="1:3">
+      <c r="A155">
         <v>702</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B155">
         <v>125.3443763000002</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="n">
+    <row r="156" spans="1:3">
+      <c r="A156">
         <v>707</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B156">
         <v>125.3462513000002</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C156">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="n">
+    <row r="157" spans="1:3">
+      <c r="A157">
         <v>709</v>
       </c>
-      <c r="B157" t="n">
+      <c r="B157">
         <v>125.3470013000002</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C157">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="n">
+    <row r="158" spans="1:3">
+      <c r="A158">
         <v>711</v>
       </c>
-      <c r="B158" t="n">
+      <c r="B158">
         <v>125.3477513000002</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C158">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="n">
+    <row r="159" spans="1:3">
+      <c r="A159">
         <v>713</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159">
         <v>125.3485013000002</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C159">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="n">
+    <row r="160" spans="1:3">
+      <c r="A160">
         <v>715</v>
       </c>
-      <c r="B160" t="n">
+      <c r="B160">
         <v>125.3492513000002</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C160">
         <v>43.89884932702704</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="n">
+    <row r="161" spans="1:3">
+      <c r="A161">
         <v>716</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B161">
         <v>125.3350013</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C161">
         <v>43.89911959729731</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="n">
+    <row r="162" spans="1:3">
+      <c r="A162">
         <v>721</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162">
         <v>125.3368763000001</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162">
         <v>43.89911959729731</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="n">
+    <row r="163" spans="1:3">
+      <c r="A163">
         <v>726</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B163">
         <v>125.3387513000001</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163">
         <v>43.89911959729731</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="n">
+    <row r="164" spans="1:3">
+      <c r="A164">
         <v>733</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B164">
         <v>125.3413763000001</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C164">
         <v>43.89911959729731</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="n">
+    <row r="165" spans="1:3">
+      <c r="A165">
         <v>738</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165">
         <v>125.3432513000002</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165">
         <v>43.89911959729731</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="n">
+    <row r="166" spans="1:3">
+      <c r="A166">
         <v>743</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166">
         <v>125.3451263000002</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C166">
         <v>43.89911959729731</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="n">
+    <row r="167" spans="1:3">
+      <c r="A167">
         <v>757</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167">
         <v>125.3357513000001</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C167">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="n">
+    <row r="168" spans="1:3">
+      <c r="A168">
         <v>762</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168">
         <v>125.3376263000001</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="n">
+    <row r="169" spans="1:3">
+      <c r="A169">
         <v>767</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169">
         <v>125.3395013000001</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="n">
+    <row r="170" spans="1:3">
+      <c r="A170">
         <v>769</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B170">
         <v>125.3402513000001</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="n">
+    <row r="171" spans="1:3">
+      <c r="A171">
         <v>774</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171">
         <v>125.3421263000001</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="n">
+    <row r="172" spans="1:3">
+      <c r="A172">
         <v>779</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B172">
         <v>125.3440013000002</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="n">
+    <row r="173" spans="1:3">
+      <c r="A173">
         <v>784</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B173">
         <v>125.3458763000002</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C173">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="n">
+    <row r="174" spans="1:3">
+      <c r="A174">
         <v>786</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B174">
         <v>125.3466263000002</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="n">
+    <row r="175" spans="1:3">
+      <c r="A175">
         <v>788</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175">
         <v>125.3473763000002</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="n">
+    <row r="176" spans="1:3">
+      <c r="A176">
         <v>790</v>
       </c>
-      <c r="B176" t="n">
+      <c r="B176">
         <v>125.3481263000002</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176">
         <v>43.89938986756758</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="n">
+    <row r="177" spans="1:3">
+      <c r="A177">
         <v>792</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B177">
         <v>125.3346263</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177">
         <v>43.89966013783785</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="n">
+    <row r="178" spans="1:3">
+      <c r="A178">
         <v>797</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178">
         <v>125.3365013000001</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178">
         <v>43.89966013783785</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="n">
+    <row r="179" spans="1:3">
+      <c r="A179">
         <v>802</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B179">
         <v>125.3383763000001</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179">
         <v>43.89966013783785</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="n">
+    <row r="180" spans="1:3">
+      <c r="A180">
         <v>809</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B180">
         <v>125.3410013000001</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180">
         <v>43.89966013783785</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="n">
+    <row r="181" spans="1:3">
+      <c r="A181">
         <v>814</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B181">
         <v>125.3428763000002</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181">
         <v>43.89966013783785</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="n">
+    <row r="182" spans="1:3">
+      <c r="A182">
         <v>819</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B182">
         <v>125.3447513000002</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182">
         <v>43.89966013783785</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="n">
+    <row r="183" spans="1:3">
+      <c r="A183">
         <v>833</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B183">
         <v>125.3353763</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="n">
+    <row r="184" spans="1:3">
+      <c r="A184">
         <v>838</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B184">
         <v>125.3372513000001</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C184">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="n">
+    <row r="185" spans="1:3">
+      <c r="A185">
         <v>843</v>
       </c>
-      <c r="B185" t="n">
+      <c r="B185">
         <v>125.3391263000001</v>
       </c>
-      <c r="C185" t="n">
+      <c r="C185">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="n">
+    <row r="186" spans="1:3">
+      <c r="A186">
         <v>845</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B186">
         <v>125.3398763000001</v>
       </c>
-      <c r="C186" t="n">
+      <c r="C186">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="n">
+    <row r="187" spans="1:3">
+      <c r="A187">
         <v>850</v>
       </c>
-      <c r="B187" t="n">
+      <c r="B187">
         <v>125.3417513000001</v>
       </c>
-      <c r="C187" t="n">
+      <c r="C187">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="n">
+    <row r="188" spans="1:3">
+      <c r="A188">
         <v>855</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B188">
         <v>125.3436263000002</v>
       </c>
-      <c r="C188" t="n">
+      <c r="C188">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="n">
+    <row r="189" spans="1:3">
+      <c r="A189">
         <v>860</v>
       </c>
-      <c r="B189" t="n">
+      <c r="B189">
         <v>125.3455013000002</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C189">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="n">
+    <row r="190" spans="1:3">
+      <c r="A190">
         <v>862</v>
       </c>
-      <c r="B190" t="n">
+      <c r="B190">
         <v>125.3462513000002</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C190">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="n">
+    <row r="191" spans="1:3">
+      <c r="A191">
         <v>864</v>
       </c>
-      <c r="B191" t="n">
+      <c r="B191">
         <v>125.3470013000002</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C191">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="n">
+    <row r="192" spans="1:3">
+      <c r="A192">
         <v>866</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B192">
         <v>125.3477513000002</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C192">
         <v>43.89993040810812</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="n">
+    <row r="193" spans="1:3">
+      <c r="A193">
         <v>868</v>
       </c>
-      <c r="B193" t="n">
+      <c r="B193">
         <v>125.3342513</v>
       </c>
-      <c r="C193" t="n">
+      <c r="C193">
         <v>43.90020067837839</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="n">
+    <row r="194" spans="1:3">
+      <c r="A194">
         <v>873</v>
       </c>
-      <c r="B194" t="n">
+      <c r="B194">
         <v>125.3361263000001</v>
       </c>
-      <c r="C194" t="n">
+      <c r="C194">
         <v>43.90020067837839</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="n">
+    <row r="195" spans="1:3">
+      <c r="A195">
         <v>878</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B195">
         <v>125.3380013000001</v>
       </c>
-      <c r="C195" t="n">
+      <c r="C195">
         <v>43.90020067837839</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="n">
+    <row r="196" spans="1:3">
+      <c r="A196">
         <v>885</v>
       </c>
-      <c r="B196" t="n">
+      <c r="B196">
         <v>125.3406263000001</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C196">
         <v>43.90020067837839</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="n">
+    <row r="197" spans="1:3">
+      <c r="A197">
         <v>890</v>
       </c>
-      <c r="B197" t="n">
+      <c r="B197">
         <v>125.3425013000002</v>
       </c>
-      <c r="C197" t="n">
+      <c r="C197">
         <v>43.90020067837839</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
+    <row r="198" spans="1:3">
+      <c r="A198">
         <v>895</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B198">
         <v>125.3443763000002</v>
       </c>
-      <c r="C198" t="n">
+      <c r="C198">
         <v>43.90020067837839</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="n">
+    <row r="199" spans="1:3">
+      <c r="A199">
         <v>908</v>
       </c>
-      <c r="B199" t="n">
+      <c r="B199">
         <v>125.3350013</v>
       </c>
-      <c r="C199" t="n">
+      <c r="C199">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="n">
+    <row r="200" spans="1:3">
+      <c r="A200">
         <v>913</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B200">
         <v>125.3368763000001</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C200">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="n">
+    <row r="201" spans="1:3">
+      <c r="A201">
         <v>918</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B201">
         <v>125.3387513000001</v>
       </c>
-      <c r="C201" t="n">
+      <c r="C201">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="n">
+    <row r="202" spans="1:3">
+      <c r="A202">
         <v>920</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202">
         <v>125.3395013000001</v>
       </c>
-      <c r="C202" t="n">
+      <c r="C202">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="n">
+    <row r="203" spans="1:3">
+      <c r="A203">
         <v>925</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203">
         <v>125.3413763000001</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C203">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="n">
+    <row r="204" spans="1:3">
+      <c r="A204">
         <v>930</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B204">
         <v>125.3432513000002</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C204">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="n">
+    <row r="205" spans="1:3">
+      <c r="A205">
         <v>935</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B205">
         <v>125.3451263000002</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C205">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="n">
+    <row r="206" spans="1:3">
+      <c r="A206">
         <v>937</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B206">
         <v>125.3458763000002</v>
       </c>
-      <c r="C206" t="n">
+      <c r="C206">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="n">
+    <row r="207" spans="1:3">
+      <c r="A207">
         <v>939</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B207">
         <v>125.3466263000002</v>
       </c>
-      <c r="C207" t="n">
+      <c r="C207">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="n">
+    <row r="208" spans="1:3">
+      <c r="A208">
         <v>941</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B208">
         <v>125.3473763000002</v>
       </c>
-      <c r="C208" t="n">
+      <c r="C208">
         <v>43.90047094864866</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="n">
+    <row r="209" spans="1:3">
+      <c r="A209">
         <v>943</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B209">
         <v>125.3335013</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C209">
         <v>43.90074121891893</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="n">
+    <row r="210" spans="1:3">
+      <c r="A210">
         <v>945</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B210">
         <v>125.3342513</v>
       </c>
-      <c r="C210" t="n">
+      <c r="C210">
         <v>43.90074121891893</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="n">
+    <row r="211" spans="1:3">
+      <c r="A211">
         <v>949</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B211">
         <v>125.3357513000001</v>
       </c>
-      <c r="C211" t="n">
+      <c r="C211">
         <v>43.90074121891893</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="n">
+    <row r="212" spans="1:3">
+      <c r="A212">
         <v>954</v>
       </c>
-      <c r="B212" t="n">
+      <c r="B212">
         <v>125.3376263000001</v>
       </c>
-      <c r="C212" t="n">
+      <c r="C212">
         <v>43.90074121891893</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="n">
+    <row r="213" spans="1:3">
+      <c r="A213">
         <v>961</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B213">
         <v>125.3402513000001</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C213">
         <v>43.90074121891893</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="n">
+    <row r="214" spans="1:3">
+      <c r="A214">
         <v>966</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214">
         <v>125.3421263000001</v>
       </c>
-      <c r="C214" t="n">
+      <c r="C214">
         <v>43.90074121891893</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="n">
+    <row r="215" spans="1:3">
+      <c r="A215">
         <v>971</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B215">
         <v>125.3440013000002</v>
       </c>
-      <c r="C215" t="n">
+      <c r="C215">
         <v>43.90074121891893</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="n">
+    <row r="216" spans="1:3">
+      <c r="A216">
         <v>985</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B216">
         <v>125.3350013</v>
       </c>
-      <c r="C216" t="n">
+      <c r="C216">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="n">
+    <row r="217" spans="1:3">
+      <c r="A217">
         <v>989</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B217">
         <v>125.3365013000001</v>
       </c>
-      <c r="C217" t="n">
+      <c r="C217">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="n">
+    <row r="218" spans="1:3">
+      <c r="A218">
         <v>994</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B218">
         <v>125.3383763000001</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C218">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="n">
+    <row r="219" spans="1:3">
+      <c r="A219">
         <v>996</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B219">
         <v>125.3391263000001</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C219">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="n">
+    <row r="220" spans="1:3">
+      <c r="A220">
         <v>1001</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B220">
         <v>125.3410013000001</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C220">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="n">
+    <row r="221" spans="1:3">
+      <c r="A221">
         <v>1006</v>
       </c>
-      <c r="B221" t="n">
+      <c r="B221">
         <v>125.3428763000002</v>
       </c>
-      <c r="C221" t="n">
+      <c r="C221">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="n">
+    <row r="222" spans="1:3">
+      <c r="A222">
         <v>1011</v>
       </c>
-      <c r="B222" t="n">
+      <c r="B222">
         <v>125.3447513000002</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C222">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="n">
+    <row r="223" spans="1:3">
+      <c r="A223">
         <v>1013</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B223">
         <v>125.3455013000002</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C223">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="n">
+    <row r="224" spans="1:3">
+      <c r="A224">
         <v>1015</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B224">
         <v>125.3462513000002</v>
       </c>
-      <c r="C224" t="n">
+      <c r="C224">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="n">
+    <row r="225" spans="1:3">
+      <c r="A225">
         <v>1017</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B225">
         <v>125.3470013000002</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C225">
         <v>43.9010114891892</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="n">
+    <row r="226" spans="1:3">
+      <c r="A226">
         <v>1018</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B226">
         <v>125.3331263</v>
       </c>
-      <c r="C226" t="n">
+      <c r="C226">
         <v>43.90128175945947</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="n">
+    <row r="227" spans="1:3">
+      <c r="A227">
         <v>1020</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227">
         <v>125.3338763</v>
       </c>
-      <c r="C227" t="n">
+      <c r="C227">
         <v>43.90128175945947</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="n">
+    <row r="228" spans="1:3">
+      <c r="A228">
         <v>1025</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B228">
         <v>125.3357513000001</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C228">
         <v>43.90128175945947</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="n">
+    <row r="229" spans="1:3">
+      <c r="A229">
         <v>1029</v>
       </c>
-      <c r="B229" t="n">
+      <c r="B229">
         <v>125.3372513000001</v>
       </c>
-      <c r="C229" t="n">
+      <c r="C229">
         <v>43.90128175945947</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="n">
+    <row r="230" spans="1:3">
+      <c r="A230">
         <v>1036</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230">
         <v>125.3398763000001</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C230">
         <v>43.90128175945947</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="n">
+    <row r="231" spans="1:3">
+      <c r="A231">
         <v>1041</v>
       </c>
-      <c r="B231" t="n">
+      <c r="B231">
         <v>125.3417513000001</v>
       </c>
-      <c r="C231" t="n">
+      <c r="C231">
         <v>43.90128175945947</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="n">
+    <row r="232" spans="1:3">
+      <c r="A232">
         <v>1046</v>
       </c>
-      <c r="B232" t="n">
+      <c r="B232">
         <v>125.3436263000002</v>
       </c>
-      <c r="C232" t="n">
+      <c r="C232">
         <v>43.90128175945947</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="n">
+    <row r="233" spans="1:3">
+      <c r="A233">
         <v>1060</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B233">
         <v>125.3346263</v>
       </c>
-      <c r="C233" t="n">
+      <c r="C233">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="n">
+    <row r="234" spans="1:3">
+      <c r="A234">
         <v>1065</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234">
         <v>125.3365013000001</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C234">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="n">
+    <row r="235" spans="1:3">
+      <c r="A235">
         <v>1069</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B235">
         <v>125.3380013000001</v>
       </c>
-      <c r="C235" t="n">
+      <c r="C235">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="n">
+    <row r="236" spans="1:3">
+      <c r="A236">
         <v>1071</v>
       </c>
-      <c r="B236" t="n">
+      <c r="B236">
         <v>125.3387513000001</v>
       </c>
-      <c r="C236" t="n">
+      <c r="C236">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="n">
+    <row r="237" spans="1:3">
+      <c r="A237">
         <v>1076</v>
       </c>
-      <c r="B237" t="n">
+      <c r="B237">
         <v>125.3406263000001</v>
       </c>
-      <c r="C237" t="n">
+      <c r="C237">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="n">
+    <row r="238" spans="1:3">
+      <c r="A238">
         <v>1081</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B238">
         <v>125.3425013000002</v>
       </c>
-      <c r="C238" t="n">
+      <c r="C238">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="n">
+    <row r="239" spans="1:3">
+      <c r="A239">
         <v>1086</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B239">
         <v>125.3443763000002</v>
       </c>
-      <c r="C239" t="n">
+      <c r="C239">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="n">
+    <row r="240" spans="1:3">
+      <c r="A240">
         <v>1088</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B240">
         <v>125.3451263000002</v>
       </c>
-      <c r="C240" t="n">
+      <c r="C240">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="n">
+    <row r="241" spans="1:3">
+      <c r="A241">
         <v>1090</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B241">
         <v>125.3458763000002</v>
       </c>
-      <c r="C241" t="n">
+      <c r="C241">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="n">
+    <row r="242" spans="1:3">
+      <c r="A242">
         <v>1092</v>
       </c>
-      <c r="B242" t="n">
+      <c r="B242">
         <v>125.3466263000002</v>
       </c>
-      <c r="C242" t="n">
+      <c r="C242">
         <v>43.90155202972974</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="n">
+    <row r="243" spans="1:3">
+      <c r="A243">
         <v>1093</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B243">
         <v>125.3327513</v>
       </c>
-      <c r="C243" t="n">
+      <c r="C243">
         <v>43.90182230000001</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="n">
+    <row r="244" spans="1:3">
+      <c r="A244">
         <v>1095</v>
       </c>
-      <c r="B244" t="n">
+      <c r="B244">
         <v>125.3335013</v>
       </c>
-      <c r="C244" t="n">
+      <c r="C244">
         <v>43.90182230000001</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="n">
+    <row r="245" spans="1:3">
+      <c r="A245">
         <v>1100</v>
       </c>
-      <c r="B245" t="n">
+      <c r="B245">
         <v>125.3353763</v>
       </c>
-      <c r="C245" t="n">
+      <c r="C245">
         <v>43.90182230000001</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="n">
+    <row r="246" spans="1:3">
+      <c r="A246">
         <v>1105</v>
       </c>
-      <c r="B246" t="n">
+      <c r="B246">
         <v>125.3372513000001</v>
       </c>
-      <c r="C246" t="n">
+      <c r="C246">
         <v>43.90182230000001</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="n">
+    <row r="247" spans="1:3">
+      <c r="A247">
         <v>1111</v>
       </c>
-      <c r="B247" t="n">
+      <c r="B247">
         <v>125.3395013000001</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C247">
         <v>43.90182230000001</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="n">
+    <row r="248" spans="1:3">
+      <c r="A248">
         <v>1116</v>
       </c>
-      <c r="B248" t="n">
+      <c r="B248">
         <v>125.3413763000001</v>
       </c>
-      <c r="C248" t="n">
+      <c r="C248">
         <v>43.90182230000001</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="n">
+    <row r="249" spans="1:3">
+      <c r="A249">
         <v>1121</v>
       </c>
-      <c r="B249" t="n">
+      <c r="B249">
         <v>125.3432513000002</v>
       </c>
-      <c r="C249" t="n">
+      <c r="C249">
         <v>43.90182230000001</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="n">
+    <row r="250" spans="1:3">
+      <c r="A250">
         <v>1135</v>
       </c>
-      <c r="B250" t="n">
+      <c r="B250">
         <v>125.3342513</v>
       </c>
-      <c r="C250" t="n">
+      <c r="C250">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="n">
+    <row r="251" spans="1:3">
+      <c r="A251">
         <v>1140</v>
       </c>
-      <c r="B251" t="n">
+      <c r="B251">
         <v>125.3361263000001</v>
       </c>
-      <c r="C251" t="n">
+      <c r="C251">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="n">
+    <row r="252" spans="1:3">
+      <c r="A252">
         <v>1145</v>
       </c>
-      <c r="B252" t="n">
+      <c r="B252">
         <v>125.3380013000001</v>
       </c>
-      <c r="C252" t="n">
+      <c r="C252">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="n">
+    <row r="253" spans="1:3">
+      <c r="A253">
         <v>1147</v>
       </c>
-      <c r="B253" t="n">
+      <c r="B253">
         <v>125.3387513000001</v>
       </c>
-      <c r="C253" t="n">
+      <c r="C253">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="n">
+    <row r="254" spans="1:3">
+      <c r="A254">
         <v>1151</v>
       </c>
-      <c r="B254" t="n">
+      <c r="B254">
         <v>125.3402513000001</v>
       </c>
-      <c r="C254" t="n">
+      <c r="C254">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="n">
+    <row r="255" spans="1:3">
+      <c r="A255">
         <v>1156</v>
       </c>
-      <c r="B255" t="n">
+      <c r="B255">
         <v>125.3421263000001</v>
       </c>
-      <c r="C255" t="n">
+      <c r="C255">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="n">
+    <row r="256" spans="1:3">
+      <c r="A256">
         <v>1161</v>
       </c>
-      <c r="B256" t="n">
+      <c r="B256">
         <v>125.3440013000002</v>
       </c>
-      <c r="C256" t="n">
+      <c r="C256">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="n">
+    <row r="257" spans="1:3">
+      <c r="A257">
         <v>1163</v>
       </c>
-      <c r="B257" t="n">
+      <c r="B257">
         <v>125.3447513000002</v>
       </c>
-      <c r="C257" t="n">
+      <c r="C257">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="n">
+    <row r="258" spans="1:3">
+      <c r="A258">
         <v>1165</v>
       </c>
-      <c r="B258" t="n">
+      <c r="B258">
         <v>125.3455013000002</v>
       </c>
-      <c r="C258" t="n">
+      <c r="C258">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="n">
+    <row r="259" spans="1:3">
+      <c r="A259">
         <v>1167</v>
       </c>
-      <c r="B259" t="n">
+      <c r="B259">
         <v>125.3462513000002</v>
       </c>
-      <c r="C259" t="n">
+      <c r="C259">
         <v>43.90209257027028</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="n">
+    <row r="260" spans="1:3">
+      <c r="A260">
         <v>1168</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B260">
         <v>125.3323763</v>
       </c>
-      <c r="C260" t="n">
+      <c r="C260">
         <v>43.90236284054055</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="n">
+    <row r="261" spans="1:3">
+      <c r="A261">
         <v>1170</v>
       </c>
-      <c r="B261" t="n">
+      <c r="B261">
         <v>125.3331263</v>
       </c>
-      <c r="C261" t="n">
+      <c r="C261">
         <v>43.90236284054055</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="n">
+    <row r="262" spans="1:3">
+      <c r="A262">
         <v>1175</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262">
         <v>125.3350013</v>
       </c>
-      <c r="C262" t="n">
+      <c r="C262">
         <v>43.90236284054055</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="n">
+    <row r="263" spans="1:3">
+      <c r="A263">
         <v>1180</v>
       </c>
-      <c r="B263" t="n">
+      <c r="B263">
         <v>125.3368763000001</v>
       </c>
-      <c r="C263" t="n">
+      <c r="C263">
         <v>43.90236284054055</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="n">
+    <row r="264" spans="1:3">
+      <c r="A264">
         <v>1187</v>
       </c>
-      <c r="B264" t="n">
+      <c r="B264">
         <v>125.3395013000001</v>
       </c>
-      <c r="C264" t="n">
+      <c r="C264">
         <v>43.90236284054055</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="n">
+    <row r="265" spans="1:3">
+      <c r="A265">
         <v>1191</v>
       </c>
-      <c r="B265" t="n">
+      <c r="B265">
         <v>125.3410013000001</v>
       </c>
-      <c r="C265" t="n">
+      <c r="C265">
         <v>43.90236284054055</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="n">
+    <row r="266" spans="1:3">
+      <c r="A266">
         <v>1196</v>
       </c>
-      <c r="B266" t="n">
+      <c r="B266">
         <v>125.3428763000002</v>
       </c>
-      <c r="C266" t="n">
+      <c r="C266">
         <v>43.90236284054055</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="n">
+    <row r="267" spans="1:3">
+      <c r="A267">
         <v>1210</v>
       </c>
-      <c r="B267" t="n">
+      <c r="B267">
         <v>125.3338763</v>
       </c>
-      <c r="C267" t="n">
+      <c r="C267">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="n">
+    <row r="268" spans="1:3">
+      <c r="A268">
         <v>1215</v>
       </c>
-      <c r="B268" t="n">
+      <c r="B268">
         <v>125.3357513000001</v>
       </c>
-      <c r="C268" t="n">
+      <c r="C268">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="n">
+    <row r="269" spans="1:3">
+      <c r="A269">
         <v>1220</v>
       </c>
-      <c r="B269" t="n">
+      <c r="B269">
         <v>125.3376263000001</v>
       </c>
-      <c r="C269" t="n">
+      <c r="C269">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="n">
+    <row r="270" spans="1:3">
+      <c r="A270">
         <v>1222</v>
       </c>
-      <c r="B270" t="n">
+      <c r="B270">
         <v>125.3383763000001</v>
       </c>
-      <c r="C270" t="n">
+      <c r="C270">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="n">
+    <row r="271" spans="1:3">
+      <c r="A271">
         <v>1227</v>
       </c>
-      <c r="B271" t="n">
+      <c r="B271">
         <v>125.3402513000001</v>
       </c>
-      <c r="C271" t="n">
+      <c r="C271">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="n">
+    <row r="272" spans="1:3">
+      <c r="A272">
         <v>1231</v>
       </c>
-      <c r="B272" t="n">
+      <c r="B272">
         <v>125.3417513000001</v>
       </c>
-      <c r="C272" t="n">
+      <c r="C272">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="n">
+    <row r="273" spans="1:3">
+      <c r="A273">
         <v>1236</v>
       </c>
-      <c r="B273" t="n">
+      <c r="B273">
         <v>125.3436263000002</v>
       </c>
-      <c r="C273" t="n">
+      <c r="C273">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="n">
+    <row r="274" spans="1:3">
+      <c r="A274">
         <v>1238</v>
       </c>
-      <c r="B274" t="n">
+      <c r="B274">
         <v>125.3443763000002</v>
       </c>
-      <c r="C274" t="n">
+      <c r="C274">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="n">
+    <row r="275" spans="1:3">
+      <c r="A275">
         <v>1240</v>
       </c>
-      <c r="B275" t="n">
+      <c r="B275">
         <v>125.3451263000002</v>
       </c>
-      <c r="C275" t="n">
+      <c r="C275">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="n">
+    <row r="276" spans="1:3">
+      <c r="A276">
         <v>1242</v>
       </c>
-      <c r="B276" t="n">
+      <c r="B276">
         <v>125.3458763000002</v>
       </c>
-      <c r="C276" t="n">
+      <c r="C276">
         <v>43.90263311081083</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="n">
+    <row r="277" spans="1:3">
+      <c r="A277">
         <v>1243</v>
       </c>
-      <c r="B277" t="n">
+      <c r="B277">
         <v>125.3323763</v>
       </c>
-      <c r="C277" t="n">
+      <c r="C277">
         <v>43.9029033810811</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="n">
+    <row r="278" spans="1:3">
+      <c r="A278">
         <v>1245</v>
       </c>
-      <c r="B278" t="n">
+      <c r="B278">
         <v>125.3331263</v>
       </c>
-      <c r="C278" t="n">
+      <c r="C278">
         <v>43.9029033810811</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="n">
+    <row r="279" spans="1:3">
+      <c r="A279">
         <v>1249</v>
       </c>
-      <c r="B279" t="n">
+      <c r="B279">
         <v>125.3346263</v>
       </c>
-      <c r="C279" t="n">
+      <c r="C279">
         <v>43.9029033810811</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="n">
+    <row r="280" spans="1:3">
+      <c r="A280">
         <v>1254</v>
       </c>
-      <c r="B280" t="n">
+      <c r="B280">
         <v>125.3365013000001</v>
       </c>
-      <c r="C280" t="n">
+      <c r="C280">
         <v>43.9029033810811</v>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="n">
+    <row r="281" spans="1:3">
+      <c r="A281">
         <v>1261</v>
       </c>
-      <c r="B281" t="n">
+      <c r="B281">
         <v>125.3391263000001</v>
       </c>
-      <c r="C281" t="n">
+      <c r="C281">
         <v>43.9029033810811</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="n">
+    <row r="282" spans="1:3">
+      <c r="A282">
         <v>1266</v>
       </c>
-      <c r="B282" t="n">
+      <c r="B282">
         <v>125.3410013000001</v>
       </c>
-      <c r="C282" t="n">
+      <c r="C282">
         <v>43.9029033810811</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="n">
+    <row r="283" spans="1:3">
+      <c r="A283">
         <v>1270</v>
       </c>
-      <c r="B283" t="n">
+      <c r="B283">
         <v>125.3425013000002</v>
       </c>
-      <c r="C283" t="n">
+      <c r="C283">
         <v>43.9029033810811</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="n">
+    <row r="284" spans="1:3">
+      <c r="A284">
         <v>1284</v>
       </c>
-      <c r="B284" t="n">
+      <c r="B284">
         <v>125.3338763</v>
       </c>
-      <c r="C284" t="n">
+      <c r="C284">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="n">
+    <row r="285" spans="1:3">
+      <c r="A285">
         <v>1288</v>
       </c>
-      <c r="B285" t="n">
+      <c r="B285">
         <v>125.3353763</v>
       </c>
-      <c r="C285" t="n">
+      <c r="C285">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="n">
+    <row r="286" spans="1:3">
+      <c r="A286">
         <v>1293</v>
       </c>
-      <c r="B286" t="n">
+      <c r="B286">
         <v>125.3372513000001</v>
       </c>
-      <c r="C286" t="n">
+      <c r="C286">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="n">
+    <row r="287" spans="1:3">
+      <c r="A287">
         <v>1295</v>
       </c>
-      <c r="B287" t="n">
+      <c r="B287">
         <v>125.3380013000001</v>
       </c>
-      <c r="C287" t="n">
+      <c r="C287">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="n">
+    <row r="288" spans="1:3">
+      <c r="A288">
         <v>1300</v>
       </c>
-      <c r="B288" t="n">
+      <c r="B288">
         <v>125.3398763000001</v>
       </c>
-      <c r="C288" t="n">
+      <c r="C288">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="n">
+    <row r="289" spans="1:3">
+      <c r="A289">
         <v>1305</v>
       </c>
-      <c r="B289" t="n">
+      <c r="B289">
         <v>125.3417513000001</v>
       </c>
-      <c r="C289" t="n">
+      <c r="C289">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="n">
+    <row r="290" spans="1:3">
+      <c r="A290">
         <v>1309</v>
       </c>
-      <c r="B290" t="n">
+      <c r="B290">
         <v>125.3432513000002</v>
       </c>
-      <c r="C290" t="n">
+      <c r="C290">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="n">
+    <row r="291" spans="1:3">
+      <c r="A291">
         <v>1311</v>
       </c>
-      <c r="B291" t="n">
+      <c r="B291">
         <v>125.3440013000002</v>
       </c>
-      <c r="C291" t="n">
+      <c r="C291">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="n">
+    <row r="292" spans="1:3">
+      <c r="A292">
         <v>1313</v>
       </c>
-      <c r="B292" t="n">
+      <c r="B292">
         <v>125.3447513000002</v>
       </c>
-      <c r="C292" t="n">
+      <c r="C292">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="n">
+    <row r="293" spans="1:3">
+      <c r="A293">
         <v>1315</v>
       </c>
-      <c r="B293" t="n">
+      <c r="B293">
         <v>125.3455013000002</v>
       </c>
-      <c r="C293" t="n">
+      <c r="C293">
         <v>43.90317365135137</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="n">
+    <row r="294" spans="1:3">
+      <c r="A294">
         <v>1317</v>
       </c>
-      <c r="B294" t="n">
+      <c r="B294">
         <v>125.3323763</v>
       </c>
-      <c r="C294" t="n">
+      <c r="C294">
         <v>43.90344392162164</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="n">
+    <row r="295" spans="1:3">
+      <c r="A295">
         <v>1319</v>
       </c>
-      <c r="B295" t="n">
+      <c r="B295">
         <v>125.3331263</v>
       </c>
-      <c r="C295" t="n">
+      <c r="C295">
         <v>43.90344392162164</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="n">
+    <row r="296" spans="1:3">
+      <c r="A296">
         <v>1323</v>
       </c>
-      <c r="B296" t="n">
+      <c r="B296">
         <v>125.3346263</v>
       </c>
-      <c r="C296" t="n">
+      <c r="C296">
         <v>43.90344392162164</v>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="n">
+    <row r="297" spans="1:3">
+      <c r="A297">
         <v>1327</v>
       </c>
-      <c r="B297" t="n">
+      <c r="B297">
         <v>125.3361263000001</v>
       </c>
-      <c r="C297" t="n">
+      <c r="C297">
         <v>43.90344392162164</v>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="n">
+    <row r="298" spans="1:3">
+      <c r="A298">
         <v>1334</v>
       </c>
-      <c r="B298" t="n">
+      <c r="B298">
         <v>125.3387513000001</v>
       </c>
-      <c r="C298" t="n">
+      <c r="C298">
         <v>43.90344392162164</v>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="n">
+    <row r="299" spans="1:3">
+      <c r="A299">
         <v>1339</v>
       </c>
-      <c r="B299" t="n">
+      <c r="B299">
         <v>125.3406263000001</v>
       </c>
-      <c r="C299" t="n">
+      <c r="C299">
         <v>43.90344392162164</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="n">
+    <row r="300" spans="1:3">
+      <c r="A300">
         <v>1344</v>
       </c>
-      <c r="B300" t="n">
+      <c r="B300">
         <v>125.3425013000002</v>
       </c>
-      <c r="C300" t="n">
+      <c r="C300">
         <v>43.90344392162164</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="n">
+    <row r="301" spans="1:3">
+      <c r="A301">
         <v>1358</v>
       </c>
-      <c r="B301" t="n">
+      <c r="B301">
         <v>125.3338763</v>
       </c>
-      <c r="C301" t="n">
+      <c r="C301">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="n">
+    <row r="302" spans="1:3">
+      <c r="A302">
         <v>1362</v>
       </c>
-      <c r="B302" t="n">
+      <c r="B302">
         <v>125.3353763</v>
       </c>
-      <c r="C302" t="n">
+      <c r="C302">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="n">
+    <row r="303" spans="1:3">
+      <c r="A303">
         <v>1366</v>
       </c>
-      <c r="B303" t="n">
+      <c r="B303">
         <v>125.3368763000001</v>
       </c>
-      <c r="C303" t="n">
+      <c r="C303">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="n">
+    <row r="304" spans="1:3">
+      <c r="A304">
         <v>1368</v>
       </c>
-      <c r="B304" t="n">
+      <c r="B304">
         <v>125.3376263000001</v>
       </c>
-      <c r="C304" t="n">
+      <c r="C304">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="n">
+    <row r="305" spans="1:3">
+      <c r="A305">
         <v>1373</v>
       </c>
-      <c r="B305" t="n">
+      <c r="B305">
         <v>125.3395013000001</v>
       </c>
-      <c r="C305" t="n">
+      <c r="C305">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="n">
+    <row r="306" spans="1:3">
+      <c r="A306">
         <v>1378</v>
       </c>
-      <c r="B306" t="n">
+      <c r="B306">
         <v>125.3413763000001</v>
       </c>
-      <c r="C306" t="n">
+      <c r="C306">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="n">
+    <row r="307" spans="1:3">
+      <c r="A307">
         <v>1383</v>
       </c>
-      <c r="B307" t="n">
+      <c r="B307">
         <v>125.3432513000002</v>
       </c>
-      <c r="C307" t="n">
+      <c r="C307">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="n">
+    <row r="308" spans="1:3">
+      <c r="A308">
         <v>1385</v>
       </c>
-      <c r="B308" t="n">
+      <c r="B308">
         <v>125.3440013000002</v>
       </c>
-      <c r="C308" t="n">
+      <c r="C308">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="n">
+    <row r="309" spans="1:3">
+      <c r="A309">
         <v>1387</v>
       </c>
-      <c r="B309" t="n">
+      <c r="B309">
         <v>125.3447513000002</v>
       </c>
-      <c r="C309" t="n">
+      <c r="C309">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="n">
+    <row r="310" spans="1:3">
+      <c r="A310">
         <v>1389</v>
       </c>
-      <c r="B310" t="n">
+      <c r="B310">
         <v>125.3455013000002</v>
       </c>
-      <c r="C310" t="n">
+      <c r="C310">
         <v>43.90371419189191</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="n">
+    <row r="311" spans="1:3">
+      <c r="A311">
         <v>1391</v>
       </c>
-      <c r="B311" t="n">
+      <c r="B311">
         <v>125.3323763</v>
       </c>
-      <c r="C311" t="n">
+      <c r="C311">
         <v>43.90398446216218</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="n">
+    <row r="312" spans="1:3">
+      <c r="A312">
         <v>1393</v>
       </c>
-      <c r="B312" t="n">
+      <c r="B312">
         <v>125.3331263</v>
       </c>
-      <c r="C312" t="n">
+      <c r="C312">
         <v>43.90398446216218</v>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="n">
+    <row r="313" spans="1:3">
+      <c r="A313">
         <v>1397</v>
       </c>
-      <c r="B313" t="n">
+      <c r="B313">
         <v>125.3346263</v>
       </c>
-      <c r="C313" t="n">
+      <c r="C313">
         <v>43.90398446216218</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="n">
+    <row r="314" spans="1:3">
+      <c r="A314">
         <v>1401</v>
       </c>
-      <c r="B314" t="n">
+      <c r="B314">
         <v>125.3361263000001</v>
       </c>
-      <c r="C314" t="n">
+      <c r="C314">
         <v>43.90398446216218</v>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="n">
+    <row r="315" spans="1:3">
+      <c r="A315">
         <v>1407</v>
       </c>
-      <c r="B315" t="n">
+      <c r="B315">
         <v>125.3383763000001</v>
       </c>
-      <c r="C315" t="n">
+      <c r="C315">
         <v>43.90398446216218</v>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="n">
+    <row r="316" spans="1:3">
+      <c r="A316">
         <v>1412</v>
       </c>
-      <c r="B316" t="n">
+      <c r="B316">
         <v>125.3402513000001</v>
       </c>
-      <c r="C316" t="n">
+      <c r="C316">
         <v>43.90398446216218</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="n">
+    <row r="317" spans="1:3">
+      <c r="A317">
         <v>1417</v>
       </c>
-      <c r="B317" t="n">
+      <c r="B317">
         <v>125.3421263000001</v>
       </c>
-      <c r="C317" t="n">
+      <c r="C317">
         <v>43.90398446216218</v>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="n">
+    <row r="318" spans="1:3">
+      <c r="A318">
         <v>1432</v>
       </c>
-      <c r="B318" t="n">
+      <c r="B318">
         <v>125.3338763</v>
       </c>
-      <c r="C318" t="n">
+      <c r="C318">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="n">
+    <row r="319" spans="1:3">
+      <c r="A319">
         <v>1436</v>
       </c>
-      <c r="B319" t="n">
+      <c r="B319">
         <v>125.3353763</v>
       </c>
-      <c r="C319" t="n">
+      <c r="C319">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="n">
+    <row r="320" spans="1:3">
+      <c r="A320">
         <v>1440</v>
       </c>
-      <c r="B320" t="n">
+      <c r="B320">
         <v>125.3368763000001</v>
       </c>
-      <c r="C320" t="n">
+      <c r="C320">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="n">
+    <row r="321" spans="1:3">
+      <c r="A321">
         <v>1442</v>
       </c>
-      <c r="B321" t="n">
+      <c r="B321">
         <v>125.3376263000001</v>
       </c>
-      <c r="C321" t="n">
+      <c r="C321">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="n">
+    <row r="322" spans="1:3">
+      <c r="A322">
         <v>1446</v>
       </c>
-      <c r="B322" t="n">
+      <c r="B322">
         <v>125.3391263000001</v>
       </c>
-      <c r="C322" t="n">
+      <c r="C322">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="n">
+    <row r="323" spans="1:3">
+      <c r="A323">
         <v>1451</v>
       </c>
-      <c r="B323" t="n">
+      <c r="B323">
         <v>125.3410013000001</v>
       </c>
-      <c r="C323" t="n">
+      <c r="C323">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="n">
+    <row r="324" spans="1:3">
+      <c r="A324">
         <v>1456</v>
       </c>
-      <c r="B324" t="n">
+      <c r="B324">
         <v>125.3428763000002</v>
       </c>
-      <c r="C324" t="n">
+      <c r="C324">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="n">
+    <row r="325" spans="1:3">
+      <c r="A325">
         <v>1458</v>
       </c>
-      <c r="B325" t="n">
+      <c r="B325">
         <v>125.3436263000002</v>
       </c>
-      <c r="C325" t="n">
+      <c r="C325">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="n">
+    <row r="326" spans="1:3">
+      <c r="A326">
         <v>1460</v>
       </c>
-      <c r="B326" t="n">
+      <c r="B326">
         <v>125.3443763000002</v>
       </c>
-      <c r="C326" t="n">
+      <c r="C326">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="n">
+    <row r="327" spans="1:3">
+      <c r="A327">
         <v>1462</v>
       </c>
-      <c r="B327" t="n">
+      <c r="B327">
         <v>125.3451263000002</v>
       </c>
-      <c r="C327" t="n">
+      <c r="C327">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="n">
+    <row r="328" spans="1:3">
+      <c r="A328">
         <v>1464</v>
       </c>
-      <c r="B328" t="n">
+      <c r="B328">
         <v>125.3458763000002</v>
       </c>
-      <c r="C328" t="n">
+      <c r="C328">
         <v>43.90425473243245</v>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="n">
+    <row r="329" spans="1:3">
+      <c r="A329">
         <v>1465</v>
       </c>
-      <c r="B329" t="n">
+      <c r="B329">
         <v>125.3323763</v>
       </c>
-      <c r="C329" t="n">
+      <c r="C329">
         <v>43.90452500270272</v>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="n">
+    <row r="330" spans="1:3">
+      <c r="A330">
         <v>1467</v>
       </c>
-      <c r="B330" t="n">
+      <c r="B330">
         <v>125.3331263</v>
       </c>
-      <c r="C330" t="n">
+      <c r="C330">
         <v>43.90452500270272</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="n">
+    <row r="331" spans="1:3">
+      <c r="A331">
         <v>1471</v>
       </c>
-      <c r="B331" t="n">
+      <c r="B331">
         <v>125.3346263</v>
       </c>
-      <c r="C331" t="n">
+      <c r="C331">
         <v>43.90452500270272</v>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="n">
+    <row r="332" spans="1:3">
+      <c r="A332">
         <v>1475</v>
       </c>
-      <c r="B332" t="n">
+      <c r="B332">
         <v>125.3361263000001</v>
       </c>
-      <c r="C332" t="n">
+      <c r="C332">
         <v>43.90452500270272</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="n">
+    <row r="333" spans="1:3">
+      <c r="A333">
         <v>1481</v>
       </c>
-      <c r="B333" t="n">
+      <c r="B333">
         <v>125.3383763000001</v>
       </c>
-      <c r="C333" t="n">
+      <c r="C333">
         <v>43.90452500270272</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="n">
+    <row r="334" spans="1:3">
+      <c r="A334">
         <v>1485</v>
       </c>
-      <c r="B334" t="n">
+      <c r="B334">
         <v>125.3398763000001</v>
       </c>
-      <c r="C334" t="n">
+      <c r="C334">
         <v>43.90452500270272</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="n">
+    <row r="335" spans="1:3">
+      <c r="A335">
         <v>1490</v>
       </c>
-      <c r="B335" t="n">
+      <c r="B335">
         <v>125.3417513000001</v>
       </c>
-      <c r="C335" t="n">
+      <c r="C335">
         <v>43.90452500270272</v>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="n">
+    <row r="336" spans="1:3">
+      <c r="A336">
         <v>1505</v>
       </c>
-      <c r="B336" t="n">
+      <c r="B336">
         <v>125.3338763</v>
       </c>
-      <c r="C336" t="n">
+      <c r="C336">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="n">
+    <row r="337" spans="1:3">
+      <c r="A337">
         <v>1509</v>
       </c>
-      <c r="B337" t="n">
+      <c r="B337">
         <v>125.3353763</v>
       </c>
-      <c r="C337" t="n">
+      <c r="C337">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="n">
+    <row r="338" spans="1:3">
+      <c r="A338">
         <v>1513</v>
       </c>
-      <c r="B338" t="n">
+      <c r="B338">
         <v>125.3368763000001</v>
       </c>
-      <c r="C338" t="n">
+      <c r="C338">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="n">
+    <row r="339" spans="1:3">
+      <c r="A339">
         <v>1515</v>
       </c>
-      <c r="B339" t="n">
+      <c r="B339">
         <v>125.3376263000001</v>
       </c>
-      <c r="C339" t="n">
+      <c r="C339">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="n">
+    <row r="340" spans="1:3">
+      <c r="A340">
         <v>1519</v>
       </c>
-      <c r="B340" t="n">
+      <c r="B340">
         <v>125.3391263000001</v>
       </c>
-      <c r="C340" t="n">
+      <c r="C340">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="n">
+    <row r="341" spans="1:3">
+      <c r="A341">
         <v>1523</v>
       </c>
-      <c r="B341" t="n">
+      <c r="B341">
         <v>125.3406263000001</v>
       </c>
-      <c r="C341" t="n">
+      <c r="C341">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="n">
+    <row r="342" spans="1:3">
+      <c r="A342">
         <v>1528</v>
       </c>
-      <c r="B342" t="n">
+      <c r="B342">
         <v>125.3425013000002</v>
       </c>
-      <c r="C342" t="n">
+      <c r="C342">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="n">
+    <row r="343" spans="1:3">
+      <c r="A343">
         <v>1530</v>
       </c>
-      <c r="B343" t="n">
+      <c r="B343">
         <v>125.3432513000002</v>
       </c>
-      <c r="C343" t="n">
+      <c r="C343">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="n">
+    <row r="344" spans="1:3">
+      <c r="A344">
         <v>1532</v>
       </c>
-      <c r="B344" t="n">
+      <c r="B344">
         <v>125.3440013000002</v>
       </c>
-      <c r="C344" t="n">
+      <c r="C344">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="n">
+    <row r="345" spans="1:3">
+      <c r="A345">
         <v>1534</v>
       </c>
-      <c r="B345" t="n">
+      <c r="B345">
         <v>125.3447513000002</v>
       </c>
-      <c r="C345" t="n">
+      <c r="C345">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="n">
+    <row r="346" spans="1:3">
+      <c r="A346">
         <v>1536</v>
       </c>
-      <c r="B346" t="n">
+      <c r="B346">
         <v>125.3455013000002</v>
       </c>
-      <c r="C346" t="n">
+      <c r="C346">
         <v>43.90479527297299</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="n">
+    <row r="347" spans="1:3">
+      <c r="A347">
         <v>1537</v>
       </c>
-      <c r="B347" t="n">
+      <c r="B347">
         <v>125.3323763</v>
       </c>
-      <c r="C347" t="n">
+      <c r="C347">
         <v>43.90506554324326</v>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="n">
+    <row r="348" spans="1:3">
+      <c r="A348">
         <v>1539</v>
       </c>
-      <c r="B348" t="n">
+      <c r="B348">
         <v>125.3331263</v>
       </c>
-      <c r="C348" t="n">
+      <c r="C348">
         <v>43.90506554324326</v>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="n">
+    <row r="349" spans="1:3">
+      <c r="A349">
         <v>1543</v>
       </c>
-      <c r="B349" t="n">
+      <c r="B349">
         <v>125.3346263</v>
       </c>
-      <c r="C349" t="n">
+      <c r="C349">
         <v>43.90506554324326</v>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="n">
+    <row r="350" spans="1:3">
+      <c r="A350">
         <v>1547</v>
       </c>
-      <c r="B350" t="n">
+      <c r="B350">
         <v>125.3361263000001</v>
       </c>
-      <c r="C350" t="n">
+      <c r="C350">
         <v>43.90506554324326</v>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="n">
+    <row r="351" spans="1:3">
+      <c r="A351">
         <v>1553</v>
       </c>
-      <c r="B351" t="n">
+      <c r="B351">
         <v>125.3383763000001</v>
       </c>
-      <c r="C351" t="n">
+      <c r="C351">
         <v>43.90506554324326</v>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="n">
+    <row r="352" spans="1:3">
+      <c r="A352">
         <v>1557</v>
       </c>
-      <c r="B352" t="n">
+      <c r="B352">
         <v>125.3398763000001</v>
       </c>
-      <c r="C352" t="n">
+      <c r="C352">
         <v>43.90506554324326</v>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="n">
+    <row r="353" spans="1:3">
+      <c r="A353">
         <v>1561</v>
       </c>
-      <c r="B353" t="n">
+      <c r="B353">
         <v>125.3413763000001</v>
       </c>
-      <c r="C353" t="n">
+      <c r="C353">
         <v>43.90506554324326</v>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="n">
+    <row r="354" spans="1:3">
+      <c r="A354">
         <v>1577</v>
       </c>
-      <c r="B354" t="n">
+      <c r="B354">
         <v>125.3338763</v>
       </c>
-      <c r="C354" t="n">
+      <c r="C354">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="n">
+    <row r="355" spans="1:3">
+      <c r="A355">
         <v>1581</v>
       </c>
-      <c r="B355" t="n">
+      <c r="B355">
         <v>125.3353763</v>
       </c>
-      <c r="C355" t="n">
+      <c r="C355">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="n">
+    <row r="356" spans="1:3">
+      <c r="A356">
         <v>1585</v>
       </c>
-      <c r="B356" t="n">
+      <c r="B356">
         <v>125.3368763000001</v>
       </c>
-      <c r="C356" t="n">
+      <c r="C356">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="n">
+    <row r="357" spans="1:3">
+      <c r="A357">
         <v>1587</v>
       </c>
-      <c r="B357" t="n">
+      <c r="B357">
         <v>125.3376263000001</v>
       </c>
-      <c r="C357" t="n">
+      <c r="C357">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="n">
+    <row r="358" spans="1:3">
+      <c r="A358">
         <v>1591</v>
       </c>
-      <c r="B358" t="n">
+      <c r="B358">
         <v>125.3391263000001</v>
       </c>
-      <c r="C358" t="n">
+      <c r="C358">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="n">
+    <row r="359" spans="1:3">
+      <c r="A359">
         <v>1595</v>
       </c>
-      <c r="B359" t="n">
+      <c r="B359">
         <v>125.3406263000001</v>
       </c>
-      <c r="C359" t="n">
+      <c r="C359">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="n">
+    <row r="360" spans="1:3">
+      <c r="A360">
         <v>1599</v>
       </c>
-      <c r="B360" t="n">
+      <c r="B360">
         <v>125.3421263000001</v>
       </c>
-      <c r="C360" t="n">
+      <c r="C360">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" t="n">
+    <row r="361" spans="1:3">
+      <c r="A361">
         <v>1601</v>
       </c>
-      <c r="B361" t="n">
+      <c r="B361">
         <v>125.3428763000002</v>
       </c>
-      <c r="C361" t="n">
+      <c r="C361">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="n">
+    <row r="362" spans="1:3">
+      <c r="A362">
         <v>1603</v>
       </c>
-      <c r="B362" t="n">
+      <c r="B362">
         <v>125.3436263000002</v>
       </c>
-      <c r="C362" t="n">
+      <c r="C362">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="n">
+    <row r="363" spans="1:3">
+      <c r="A363">
         <v>1605</v>
       </c>
-      <c r="B363" t="n">
+      <c r="B363">
         <v>125.3443763000002</v>
       </c>
-      <c r="C363" t="n">
+      <c r="C363">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="n">
+    <row r="364" spans="1:3">
+      <c r="A364">
         <v>1607</v>
       </c>
-      <c r="B364" t="n">
+      <c r="B364">
         <v>125.3451263000002</v>
       </c>
-      <c r="C364" t="n">
+      <c r="C364">
         <v>43.90533581351353</v>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="n">
+    <row r="365" spans="1:3">
+      <c r="A365">
         <v>1609</v>
       </c>
-      <c r="B365" t="n">
+      <c r="B365">
         <v>125.3323763</v>
       </c>
-      <c r="C365" t="n">
+      <c r="C365">
         <v>43.9056060837838</v>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="n">
+    <row r="366" spans="1:3">
+      <c r="A366">
         <v>1611</v>
       </c>
-      <c r="B366" t="n">
+      <c r="B366">
         <v>125.3331263</v>
       </c>
-      <c r="C366" t="n">
+      <c r="C366">
         <v>43.9056060837838</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="n">
+    <row r="367" spans="1:3">
+      <c r="A367">
         <v>1615</v>
       </c>
-      <c r="B367" t="n">
+      <c r="B367">
         <v>125.3346263</v>
       </c>
-      <c r="C367" t="n">
+      <c r="C367">
         <v>43.9056060837838</v>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="n">
+    <row r="368" spans="1:3">
+      <c r="A368">
         <v>1619</v>
       </c>
-      <c r="B368" t="n">
+      <c r="B368">
         <v>125.3361263000001</v>
       </c>
-      <c r="C368" t="n">
+      <c r="C368">
         <v>43.9056060837838</v>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="n">
+    <row r="369" spans="1:3">
+      <c r="A369">
         <v>1625</v>
       </c>
-      <c r="B369" t="n">
+      <c r="B369">
         <v>125.3383763000001</v>
       </c>
-      <c r="C369" t="n">
+      <c r="C369">
         <v>43.9056060837838</v>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="n">
+    <row r="370" spans="1:3">
+      <c r="A370">
         <v>1629</v>
       </c>
-      <c r="B370" t="n">
+      <c r="B370">
         <v>125.3398763000001</v>
       </c>
-      <c r="C370" t="n">
+      <c r="C370">
         <v>43.9056060837838</v>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="n">
+    <row r="371" spans="1:3">
+      <c r="A371">
         <v>1633</v>
       </c>
-      <c r="B371" t="n">
+      <c r="B371">
         <v>125.3413763000001</v>
       </c>
-      <c r="C371" t="n">
+      <c r="C371">
         <v>43.9056060837838</v>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="n">
+    <row r="372" spans="1:3">
+      <c r="A372">
         <v>1649</v>
       </c>
-      <c r="B372" t="n">
+      <c r="B372">
         <v>125.3338763</v>
       </c>
-      <c r="C372" t="n">
+      <c r="C372">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="n">
+    <row r="373" spans="1:3">
+      <c r="A373">
         <v>1653</v>
       </c>
-      <c r="B373" t="n">
+      <c r="B373">
         <v>125.3353763</v>
       </c>
-      <c r="C373" t="n">
+      <c r="C373">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="n">
+    <row r="374" spans="1:3">
+      <c r="A374">
         <v>1657</v>
       </c>
-      <c r="B374" t="n">
+      <c r="B374">
         <v>125.3368763000001</v>
       </c>
-      <c r="C374" t="n">
+      <c r="C374">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="n">
+    <row r="375" spans="1:3">
+      <c r="A375">
         <v>1659</v>
       </c>
-      <c r="B375" t="n">
+      <c r="B375">
         <v>125.3376263000001</v>
       </c>
-      <c r="C375" t="n">
+      <c r="C375">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="n">
+    <row r="376" spans="1:3">
+      <c r="A376">
         <v>1663</v>
       </c>
-      <c r="B376" t="n">
+      <c r="B376">
         <v>125.3391263000001</v>
       </c>
-      <c r="C376" t="n">
+      <c r="C376">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="n">
+    <row r="377" spans="1:3">
+      <c r="A377">
         <v>1667</v>
       </c>
-      <c r="B377" t="n">
+      <c r="B377">
         <v>125.3406263000001</v>
       </c>
-      <c r="C377" t="n">
+      <c r="C377">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="n">
+    <row r="378" spans="1:3">
+      <c r="A378">
         <v>1671</v>
       </c>
-      <c r="B378" t="n">
+      <c r="B378">
         <v>125.3421263000001</v>
       </c>
-      <c r="C378" t="n">
+      <c r="C378">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="n">
+    <row r="379" spans="1:3">
+      <c r="A379">
         <v>1673</v>
       </c>
-      <c r="B379" t="n">
+      <c r="B379">
         <v>125.3428763000002</v>
       </c>
-      <c r="C379" t="n">
+      <c r="C379">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="n">
+    <row r="380" spans="1:3">
+      <c r="A380">
         <v>1675</v>
       </c>
-      <c r="B380" t="n">
+      <c r="B380">
         <v>125.3436263000002</v>
       </c>
-      <c r="C380" t="n">
+      <c r="C380">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="n">
+    <row r="381" spans="1:3">
+      <c r="A381">
         <v>1677</v>
       </c>
-      <c r="B381" t="n">
+      <c r="B381">
         <v>125.3443763000002</v>
       </c>
-      <c r="C381" t="n">
+      <c r="C381">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="n">
+    <row r="382" spans="1:3">
+      <c r="A382">
         <v>1679</v>
       </c>
-      <c r="B382" t="n">
+      <c r="B382">
         <v>125.3451263000002</v>
       </c>
-      <c r="C382" t="n">
+      <c r="C382">
         <v>43.90587635405407</v>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="n">
+    <row r="383" spans="1:3">
+      <c r="A383">
         <v>1681</v>
       </c>
-      <c r="B383" t="n">
+      <c r="B383">
         <v>125.3323763</v>
       </c>
-      <c r="C383" t="n">
+      <c r="C383">
         <v>43.90614662432434</v>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="n">
+    <row r="384" spans="1:3">
+      <c r="A384">
         <v>1683</v>
       </c>
-      <c r="B384" t="n">
+      <c r="B384">
         <v>125.3331263</v>
       </c>
-      <c r="C384" t="n">
+      <c r="C384">
         <v>43.90614662432434</v>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="n">
+    <row r="385" spans="1:3">
+      <c r="A385">
         <v>1687</v>
       </c>
-      <c r="B385" t="n">
+      <c r="B385">
         <v>125.3346263</v>
       </c>
-      <c r="C385" t="n">
+      <c r="C385">
         <v>43.90614662432434</v>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="n">
+    <row r="386" spans="1:3">
+      <c r="A386">
         <v>1691</v>
       </c>
-      <c r="B386" t="n">
+      <c r="B386">
         <v>125.3361263000001</v>
       </c>
-      <c r="C386" t="n">
+      <c r="C386">
         <v>43.90614662432434</v>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="n">
+    <row r="387" spans="1:3">
+      <c r="A387">
         <v>1697</v>
       </c>
-      <c r="B387" t="n">
+      <c r="B387">
         <v>125.3383763000001</v>
       </c>
-      <c r="C387" t="n">
+      <c r="C387">
         <v>43.90614662432434</v>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="n">
+    <row r="388" spans="1:3">
+      <c r="A388">
         <v>1701</v>
       </c>
-      <c r="B388" t="n">
+      <c r="B388">
         <v>125.3398763000001</v>
       </c>
-      <c r="C388" t="n">
+      <c r="C388">
         <v>43.90614662432434</v>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="n">
+    <row r="389" spans="1:3">
+      <c r="A389">
         <v>1705</v>
       </c>
-      <c r="B389" t="n">
+      <c r="B389">
         <v>125.3413763000001</v>
       </c>
-      <c r="C389" t="n">
+      <c r="C389">
         <v>43.90614662432434</v>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="n">
+    <row r="390" spans="1:3">
+      <c r="A390">
         <v>1720</v>
       </c>
-      <c r="B390" t="n">
+      <c r="B390">
         <v>125.3338763</v>
       </c>
-      <c r="C390" t="n">
+      <c r="C390">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="n">
+    <row r="391" spans="1:3">
+      <c r="A391">
         <v>1724</v>
       </c>
-      <c r="B391" t="n">
+      <c r="B391">
         <v>125.3353763</v>
       </c>
-      <c r="C391" t="n">
+      <c r="C391">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="n">
+    <row r="392" spans="1:3">
+      <c r="A392">
         <v>1728</v>
       </c>
-      <c r="B392" t="n">
+      <c r="B392">
         <v>125.3368763000001</v>
       </c>
-      <c r="C392" t="n">
+      <c r="C392">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="n">
+    <row r="393" spans="1:3">
+      <c r="A393">
         <v>1730</v>
       </c>
-      <c r="B393" t="n">
+      <c r="B393">
         <v>125.3376263000001</v>
       </c>
-      <c r="C393" t="n">
+      <c r="C393">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="n">
+    <row r="394" spans="1:3">
+      <c r="A394">
         <v>1734</v>
       </c>
-      <c r="B394" t="n">
+      <c r="B394">
         <v>125.3391263000001</v>
       </c>
-      <c r="C394" t="n">
+      <c r="C394">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="n">
+    <row r="395" spans="1:3">
+      <c r="A395">
         <v>1738</v>
       </c>
-      <c r="B395" t="n">
+      <c r="B395">
         <v>125.3406263000001</v>
       </c>
-      <c r="C395" t="n">
+      <c r="C395">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="n">
+    <row r="396" spans="1:3">
+      <c r="A396">
         <v>1742</v>
       </c>
-      <c r="B396" t="n">
+      <c r="B396">
         <v>125.3421263000001</v>
       </c>
-      <c r="C396" t="n">
+      <c r="C396">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="n">
+    <row r="397" spans="1:3">
+      <c r="A397">
         <v>1744</v>
       </c>
-      <c r="B397" t="n">
+      <c r="B397">
         <v>125.3428763000002</v>
       </c>
-      <c r="C397" t="n">
+      <c r="C397">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="n">
+    <row r="398" spans="1:3">
+      <c r="A398">
         <v>1746</v>
       </c>
-      <c r="B398" t="n">
+      <c r="B398">
         <v>125.3436263000002</v>
       </c>
-      <c r="C398" t="n">
+      <c r="C398">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="n">
+    <row r="399" spans="1:3">
+      <c r="A399">
         <v>1748</v>
       </c>
-      <c r="B399" t="n">
+      <c r="B399">
         <v>125.3443763000002</v>
       </c>
-      <c r="C399" t="n">
+      <c r="C399">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="n">
+    <row r="400" spans="1:3">
+      <c r="A400">
         <v>1750</v>
       </c>
-      <c r="B400" t="n">
+      <c r="B400">
         <v>125.3451263000002</v>
       </c>
-      <c r="C400" t="n">
+      <c r="C400">
         <v>43.90641689459461</v>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="n">
+    <row r="401" spans="1:3">
+      <c r="A401">
         <v>1751</v>
       </c>
-      <c r="B401" t="n">
+      <c r="B401">
         <v>125.3323763</v>
       </c>
-      <c r="C401" t="n">
+      <c r="C401">
         <v>43.90668716486488</v>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="n">
+    <row r="402" spans="1:3">
+      <c r="A402">
         <v>1753</v>
       </c>
-      <c r="B402" t="n">
+      <c r="B402">
         <v>125.3331263</v>
       </c>
-      <c r="C402" t="n">
+      <c r="C402">
         <v>43.90668716486488</v>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="n">
+    <row r="403" spans="1:3">
+      <c r="A403">
         <v>1757</v>
       </c>
-      <c r="B403" t="n">
+      <c r="B403">
         <v>125.3346263</v>
       </c>
-      <c r="C403" t="n">
+      <c r="C403">
         <v>43.90668716486488</v>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="n">
+    <row r="404" spans="1:3">
+      <c r="A404">
         <v>1761</v>
       </c>
-      <c r="B404" t="n">
+      <c r="B404">
         <v>125.3361263000001</v>
       </c>
-      <c r="C404" t="n">
+      <c r="C404">
         <v>43.90668716486488</v>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="n">
+    <row r="405" spans="1:3">
+      <c r="A405">
         <v>1767</v>
       </c>
-      <c r="B405" t="n">
+      <c r="B405">
         <v>125.3383763000001</v>
       </c>
-      <c r="C405" t="n">
+      <c r="C405">
         <v>43.90668716486488</v>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="n">
+    <row r="406" spans="1:3">
+      <c r="A406">
         <v>1771</v>
       </c>
-      <c r="B406" t="n">
+      <c r="B406">
         <v>125.3398763000001</v>
       </c>
-      <c r="C406" t="n">
+      <c r="C406">
         <v>43.90668716486488</v>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="n">
+    <row r="407" spans="1:3">
+      <c r="A407">
         <v>1775</v>
       </c>
-      <c r="B407" t="n">
+      <c r="B407">
         <v>125.3413763000001</v>
       </c>
-      <c r="C407" t="n">
+      <c r="C407">
         <v>43.90668716486488</v>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" t="n">
+    <row r="408" spans="1:3">
+      <c r="A408">
         <v>1789</v>
       </c>
-      <c r="B408" t="n">
+      <c r="B408">
         <v>125.3338763</v>
       </c>
-      <c r="C408" t="n">
+      <c r="C408">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="n">
+    <row r="409" spans="1:3">
+      <c r="A409">
         <v>1793</v>
       </c>
-      <c r="B409" t="n">
+      <c r="B409">
         <v>125.3353763</v>
       </c>
-      <c r="C409" t="n">
+      <c r="C409">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="n">
+    <row r="410" spans="1:3">
+      <c r="A410">
         <v>1797</v>
       </c>
-      <c r="B410" t="n">
+      <c r="B410">
         <v>125.3368763000001</v>
       </c>
-      <c r="C410" t="n">
+      <c r="C410">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" t="n">
+    <row r="411" spans="1:3">
+      <c r="A411">
         <v>1799</v>
       </c>
-      <c r="B411" t="n">
+      <c r="B411">
         <v>125.3376263000001</v>
       </c>
-      <c r="C411" t="n">
+      <c r="C411">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" t="n">
+    <row r="412" spans="1:3">
+      <c r="A412">
         <v>1803</v>
       </c>
-      <c r="B412" t="n">
+      <c r="B412">
         <v>125.3391263000001</v>
       </c>
-      <c r="C412" t="n">
+      <c r="C412">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" t="n">
+    <row r="413" spans="1:3">
+      <c r="A413">
         <v>1807</v>
       </c>
-      <c r="B413" t="n">
+      <c r="B413">
         <v>125.3406263000001</v>
       </c>
-      <c r="C413" t="n">
+      <c r="C413">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" t="n">
+    <row r="414" spans="1:3">
+      <c r="A414">
         <v>1811</v>
       </c>
-      <c r="B414" t="n">
+      <c r="B414">
         <v>125.3421263000001</v>
       </c>
-      <c r="C414" t="n">
+      <c r="C414">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="n">
+    <row r="415" spans="1:3">
+      <c r="A415">
         <v>1813</v>
       </c>
-      <c r="B415" t="n">
+      <c r="B415">
         <v>125.3428763000002</v>
       </c>
-      <c r="C415" t="n">
+      <c r="C415">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="416">
-      <c r="A416" t="n">
+    <row r="416" spans="1:3">
+      <c r="A416">
         <v>1815</v>
       </c>
-      <c r="B416" t="n">
+      <c r="B416">
         <v>125.3436263000002</v>
       </c>
-      <c r="C416" t="n">
+      <c r="C416">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="417">
-      <c r="A417" t="n">
+    <row r="417" spans="1:3">
+      <c r="A417">
         <v>1817</v>
       </c>
-      <c r="B417" t="n">
+      <c r="B417">
         <v>125.3443763000002</v>
       </c>
-      <c r="C417" t="n">
+      <c r="C417">
         <v>43.90695743513515</v>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="n">
+    <row r="418" spans="1:3">
+      <c r="A418">
         <v>1819</v>
       </c>
-      <c r="B418" t="n">
+      <c r="B418">
         <v>125.3323763</v>
       </c>
-      <c r="C418" t="n">
+      <c r="C418">
         <v>43.90722770540543</v>
       </c>
     </row>
-    <row r="419">
-      <c r="A419" t="n">
+    <row r="419" spans="1:3">
+      <c r="A419">
         <v>1821</v>
       </c>
-      <c r="B419" t="n">
+      <c r="B419">
         <v>125.3331263</v>
       </c>
-      <c r="C419" t="n">
+      <c r="C419">
         <v>43.90722770540543</v>
       </c>
     </row>
-    <row r="420">
-      <c r="A420" t="n">
+    <row r="420" spans="1:3">
+      <c r="A420">
         <v>1825</v>
       </c>
-      <c r="B420" t="n">
+      <c r="B420">
         <v>125.3346263</v>
       </c>
-      <c r="C420" t="n">
+      <c r="C420">
         <v>43.90722770540543</v>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="n">
+    <row r="421" spans="1:3">
+      <c r="A421">
         <v>1829</v>
       </c>
-      <c r="B421" t="n">
+      <c r="B421">
         <v>125.3361263000001</v>
       </c>
-      <c r="C421" t="n">
+      <c r="C421">
         <v>43.90722770540543</v>
       </c>
     </row>
-    <row r="422">
-      <c r="A422" t="n">
+    <row r="422" spans="1:3">
+      <c r="A422">
         <v>1835</v>
       </c>
-      <c r="B422" t="n">
+      <c r="B422">
         <v>125.3383763000001</v>
       </c>
-      <c r="C422" t="n">
+      <c r="C422">
         <v>43.90722770540543</v>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="n">
+    <row r="423" spans="1:3">
+      <c r="A423">
         <v>1839</v>
       </c>
-      <c r="B423" t="n">
+      <c r="B423">
         <v>125.3398763000001</v>
       </c>
-      <c r="C423" t="n">
+      <c r="C423">
         <v>43.90722770540543</v>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" t="n">
+    <row r="424" spans="1:3">
+      <c r="A424">
         <v>1843</v>
       </c>
-      <c r="B424" t="n">
+      <c r="B424">
         <v>125.3413763000001</v>
       </c>
-      <c r="C424" t="n">
+      <c r="C424">
         <v>43.90722770540543</v>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="n">
+    <row r="425" spans="1:3">
+      <c r="A425">
         <v>1856</v>
       </c>
-      <c r="B425" t="n">
+      <c r="B425">
         <v>125.3338763</v>
       </c>
-      <c r="C425" t="n">
+      <c r="C425">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" t="n">
+    <row r="426" spans="1:3">
+      <c r="A426">
         <v>1860</v>
       </c>
-      <c r="B426" t="n">
+      <c r="B426">
         <v>125.3353763</v>
       </c>
-      <c r="C426" t="n">
+      <c r="C426">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="427">
-      <c r="A427" t="n">
+    <row r="427" spans="1:3">
+      <c r="A427">
         <v>1864</v>
       </c>
-      <c r="B427" t="n">
+      <c r="B427">
         <v>125.3368763000001</v>
       </c>
-      <c r="C427" t="n">
+      <c r="C427">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="428">
-      <c r="A428" t="n">
+    <row r="428" spans="1:3">
+      <c r="A428">
         <v>1866</v>
       </c>
-      <c r="B428" t="n">
+      <c r="B428">
         <v>125.3376263000001</v>
       </c>
-      <c r="C428" t="n">
+      <c r="C428">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="429">
-      <c r="A429" t="n">
+    <row r="429" spans="1:3">
+      <c r="A429">
         <v>1870</v>
       </c>
-      <c r="B429" t="n">
+      <c r="B429">
         <v>125.3391263000001</v>
       </c>
-      <c r="C429" t="n">
+      <c r="C429">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" t="n">
+    <row r="430" spans="1:3">
+      <c r="A430">
         <v>1874</v>
       </c>
-      <c r="B430" t="n">
+      <c r="B430">
         <v>125.3406263000001</v>
       </c>
-      <c r="C430" t="n">
+      <c r="C430">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="431">
-      <c r="A431" t="n">
+    <row r="431" spans="1:3">
+      <c r="A431">
         <v>1878</v>
       </c>
-      <c r="B431" t="n">
+      <c r="B431">
         <v>125.3421263000001</v>
       </c>
-      <c r="C431" t="n">
+      <c r="C431">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="n">
+    <row r="432" spans="1:3">
+      <c r="A432">
         <v>1880</v>
       </c>
-      <c r="B432" t="n">
+      <c r="B432">
         <v>125.3428763000002</v>
       </c>
-      <c r="C432" t="n">
+      <c r="C432">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" t="n">
+    <row r="433" spans="1:3">
+      <c r="A433">
         <v>1882</v>
       </c>
-      <c r="B433" t="n">
+      <c r="B433">
         <v>125.3436263000002</v>
       </c>
-      <c r="C433" t="n">
+      <c r="C433">
         <v>43.9074979756757</v>
       </c>
     </row>
-    <row r="434">
-      <c r="A434" t="n">
+    <row r="434" spans="1:3">
+      <c r="A434">
         <v>1884</v>
       </c>
-      <c r="B434" t="n">
+      <c r="B434">
         <v>125.3323763</v>
       </c>
-      <c r="C434" t="n">
+      <c r="C434">
         <v>43.90776824594597</v>
       </c>
     </row>
-    <row r="435">
-      <c r="A435" t="n">
+    <row r="435" spans="1:3">
+      <c r="A435">
         <v>1886</v>
       </c>
-      <c r="B435" t="n">
+      <c r="B435">
         <v>125.3331263</v>
       </c>
-      <c r="C435" t="n">
+      <c r="C435">
         <v>43.90776824594597</v>
       </c>
     </row>
-    <row r="436">
-      <c r="A436" t="n">
+    <row r="436" spans="1:3">
+      <c r="A436">
         <v>1890</v>
       </c>
-      <c r="B436" t="n">
+      <c r="B436">
         <v>125.3346263</v>
       </c>
-      <c r="C436" t="n">
+      <c r="C436">
         <v>43.90776824594597</v>
       </c>
     </row>
-    <row r="437">
-      <c r="A437" t="n">
+    <row r="437" spans="1:3">
+      <c r="A437">
         <v>1894</v>
       </c>
-      <c r="B437" t="n">
+      <c r="B437">
         <v>125.3361263000001</v>
       </c>
-      <c r="C437" t="n">
+      <c r="C437">
         <v>43.90776824594597</v>
       </c>
     </row>
-    <row r="438">
-      <c r="A438" t="n">
+    <row r="438" spans="1:3">
+      <c r="A438">
         <v>1900</v>
       </c>
-      <c r="B438" t="n">
+      <c r="B438">
         <v>125.3383763000001</v>
       </c>
-      <c r="C438" t="n">
+      <c r="C438">
         <v>43.90776824594597</v>
       </c>
     </row>
-    <row r="439">
-      <c r="A439" t="n">
+    <row r="439" spans="1:3">
+      <c r="A439">
         <v>1904</v>
       </c>
-      <c r="B439" t="n">
+      <c r="B439">
         <v>125.3398763000001</v>
       </c>
-      <c r="C439" t="n">
+      <c r="C439">
         <v>43.90776824594597</v>
       </c>
     </row>
-    <row r="440">
-      <c r="A440" t="n">
+    <row r="440" spans="1:3">
+      <c r="A440">
         <v>1908</v>
       </c>
-      <c r="B440" t="n">
+      <c r="B440">
         <v>125.3413763000001</v>
       </c>
-      <c r="C440" t="n">
+      <c r="C440">
         <v>43.90776824594597</v>
       </c>
     </row>
-    <row r="441">
-      <c r="A441" t="n">
+    <row r="441" spans="1:3">
+      <c r="A441">
         <v>1919</v>
       </c>
-      <c r="B441" t="n">
+      <c r="B441">
         <v>125.3338763</v>
       </c>
-      <c r="C441" t="n">
+      <c r="C441">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="442">
-      <c r="A442" t="n">
+    <row r="442" spans="1:3">
+      <c r="A442">
         <v>1923</v>
       </c>
-      <c r="B442" t="n">
+      <c r="B442">
         <v>125.3353763</v>
       </c>
-      <c r="C442" t="n">
+      <c r="C442">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="443">
-      <c r="A443" t="n">
+    <row r="443" spans="1:3">
+      <c r="A443">
         <v>1927</v>
       </c>
-      <c r="B443" t="n">
+      <c r="B443">
         <v>125.3368763000001</v>
       </c>
-      <c r="C443" t="n">
+      <c r="C443">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="444">
-      <c r="A444" t="n">
+    <row r="444" spans="1:3">
+      <c r="A444">
         <v>1929</v>
       </c>
-      <c r="B444" t="n">
+      <c r="B444">
         <v>125.3376263000001</v>
       </c>
-      <c r="C444" t="n">
+      <c r="C444">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="445">
-      <c r="A445" t="n">
+    <row r="445" spans="1:3">
+      <c r="A445">
         <v>1933</v>
       </c>
-      <c r="B445" t="n">
+      <c r="B445">
         <v>125.3391263000001</v>
       </c>
-      <c r="C445" t="n">
+      <c r="C445">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="446">
-      <c r="A446" t="n">
+    <row r="446" spans="1:3">
+      <c r="A446">
         <v>1937</v>
       </c>
-      <c r="B446" t="n">
+      <c r="B446">
         <v>125.3406263000001</v>
       </c>
-      <c r="C446" t="n">
+      <c r="C446">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="447">
-      <c r="A447" t="n">
+    <row r="447" spans="1:3">
+      <c r="A447">
         <v>1941</v>
       </c>
-      <c r="B447" t="n">
+      <c r="B447">
         <v>125.3421263000001</v>
       </c>
-      <c r="C447" t="n">
+      <c r="C447">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="448">
-      <c r="A448" t="n">
+    <row r="448" spans="1:3">
+      <c r="A448">
         <v>1943</v>
       </c>
-      <c r="B448" t="n">
+      <c r="B448">
         <v>125.3428763000002</v>
       </c>
-      <c r="C448" t="n">
+      <c r="C448">
         <v>43.90803851621624</v>
       </c>
     </row>
-    <row r="449">
-      <c r="A449" t="n">
+    <row r="449" spans="1:3">
+      <c r="A449">
         <v>1945</v>
       </c>
-      <c r="B449" t="n">
+      <c r="B449">
         <v>125.3323763</v>
       </c>
-      <c r="C449" t="n">
+      <c r="C449">
         <v>43.90830878648651</v>
       </c>
     </row>
-    <row r="450">
-      <c r="A450" t="n">
+    <row r="450" spans="1:3">
+      <c r="A450">
         <v>1947</v>
       </c>
-      <c r="B450" t="n">
+      <c r="B450">
         <v>125.3331263</v>
       </c>
-      <c r="C450" t="n">
+      <c r="C450">
         <v>43.90830878648651</v>
       </c>
     </row>
-    <row r="451">
-      <c r="A451" t="n">
+    <row r="451" spans="1:3">
+      <c r="A451">
         <v>1951</v>
       </c>
-      <c r="B451" t="n">
+      <c r="B451">
         <v>125.3346263</v>
       </c>
-      <c r="C451" t="n">
+      <c r="C451">
         <v>43.90830878648651</v>
       </c>
     </row>
-    <row r="452">
-      <c r="A452" t="n">
+    <row r="452" spans="1:3">
+      <c r="A452">
         <v>1955</v>
       </c>
-      <c r="B452" t="n">
+      <c r="B452">
         <v>125.3361263000001</v>
       </c>
-      <c r="C452" t="n">
+      <c r="C452">
         <v>43.90830878648651</v>
       </c>
     </row>
-    <row r="453">
-      <c r="A453" t="n">
+    <row r="453" spans="1:3">
+      <c r="A453">
         <v>1961</v>
       </c>
-      <c r="B453" t="n">
+      <c r="B453">
         <v>125.3383763000001</v>
       </c>
-      <c r="C453" t="n">
+      <c r="C453">
         <v>43.90830878648651</v>
       </c>
     </row>
-    <row r="454">
-      <c r="A454" t="n">
+    <row r="454" spans="1:3">
+      <c r="A454">
         <v>1965</v>
       </c>
-      <c r="B454" t="n">
+      <c r="B454">
         <v>125.3398763000001</v>
       </c>
-      <c r="C454" t="n">
+      <c r="C454">
         <v>43.90830878648651</v>
       </c>
     </row>
-    <row r="455">
-      <c r="A455" t="n">
+    <row r="455" spans="1:3">
+      <c r="A455">
         <v>1969</v>
       </c>
-      <c r="B455" t="n">
+      <c r="B455">
         <v>125.3413763000001</v>
       </c>
-      <c r="C455" t="n">
+      <c r="C455">
         <v>43.90830878648651</v>
       </c>
     </row>
-    <row r="456">
-      <c r="A456" t="n">
+    <row r="456" spans="1:3">
+      <c r="A456">
         <v>1973</v>
       </c>
-      <c r="B456" t="n">
+      <c r="B456">
         <v>125.3372513000001</v>
       </c>
-      <c r="C456" t="n">
+      <c r="C456">
         <v>43.90857905675678</v>
       </c>
     </row>
-    <row r="457">
-      <c r="A457" t="n">
+    <row r="457" spans="1:3">
+      <c r="A457">
         <v>1978</v>
       </c>
-      <c r="B457" t="n">
+      <c r="B457">
         <v>125.3391263000001</v>
       </c>
-      <c r="C457" t="n">
+      <c r="C457">
         <v>43.90857905675678</v>
       </c>
     </row>
-    <row r="458">
-      <c r="A458" t="n">
+    <row r="458" spans="1:3">
+      <c r="A458">
         <v>1982</v>
       </c>
-      <c r="B458" t="n">
+      <c r="B458">
         <v>125.3406263000001</v>
       </c>
-      <c r="C458" t="n">
+      <c r="C458">
         <v>43.90857905675678</v>
       </c>
     </row>
-    <row r="459">
-      <c r="A459" t="n">
+    <row r="459" spans="1:3">
+      <c r="A459">
         <v>1986</v>
       </c>
-      <c r="B459" t="n">
+      <c r="B459">
         <v>125.3421263000001</v>
       </c>
-      <c r="C459" t="n">
+      <c r="C459">
         <v>43.90857905675678</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>